--- a/data/trans_camb/PCS12_SP_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Edad-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 7,94</t>
+          <t>-3,8; 7,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,71</t>
+          <t>-9,22; 1,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,42; 5,45</t>
+          <t>-9,88; 5,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 5,99</t>
+          <t>-5,72; 5,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 0,24</t>
+          <t>-12,08; -1,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,99; -1,72</t>
+          <t>-16,85; -1,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 5,05</t>
+          <t>-3,04; 5,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -1,29</t>
+          <t>-9,17; -1,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,17</t>
+          <t>-11,62; -0,28</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 40,06</t>
+          <t>-15,34; 36,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,61; 9,39</t>
+          <t>-36,77; 7,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,69; 27,5</t>
+          <t>-41,15; 26,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 23,84</t>
+          <t>-18,37; 22,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 1,27</t>
+          <t>-40,07; -4,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,88; -5,79</t>
+          <t>-56,46; -6,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 21,69</t>
+          <t>-11,32; 22,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,99; -5,38</t>
+          <t>-35,12; -6,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-44,5; -1,17</t>
+          <t>-43,16; -0,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 9,15</t>
+          <t>-1,07; 9,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,55; 2,99</t>
+          <t>-6,84; 3,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 13,45</t>
+          <t>0,03; 13,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 1,17</t>
+          <t>-9,96; 1,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,14; -10,72</t>
+          <t>-21,36; -10,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,58; -6,81</t>
+          <t>-23,67; -6,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 4,09</t>
+          <t>-3,54; 4,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,91; -4,81</t>
+          <t>-11,89; -4,92</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 1,96</t>
+          <t>-10,56; 1,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 43,43</t>
+          <t>-4,16; 42,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,83; 13,38</t>
+          <t>-26,8; 14,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 60,43</t>
+          <t>-0,3; 62,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 3,55</t>
+          <t>-24,09; 2,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,68; -28,96</t>
+          <t>-50,73; -29,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,66; -17,99</t>
+          <t>-59,78; -17,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 13,88</t>
+          <t>-10,61; 14,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,46; -16,17</t>
+          <t>-36,29; -16,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 6,19</t>
+          <t>-32,54; 5,57</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 7,15</t>
+          <t>-3,5; 6,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-14,91; -5,01</t>
+          <t>-15,43; -5,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 5,58</t>
+          <t>-5,57; 5,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 1,16</t>
+          <t>-9,35; 1,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,65; -8,85</t>
+          <t>-19,98; -8,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,71; -6,36</t>
+          <t>-16,92; -6,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,93</t>
+          <t>-5,3; 2,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-15,91; -8,87</t>
+          <t>-16,01; -8,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -2,22</t>
+          <t>-10,27; -2,4</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 22,56</t>
+          <t>-9,75; 22,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-40,41; -14,85</t>
+          <t>-41,93; -15,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,54; 17,27</t>
+          <t>-15,34; 17,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 2,54</t>
+          <t>-18,43; 3,66</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-38,21; -19,58</t>
+          <t>-39,27; -19,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,98; -14,41</t>
+          <t>-32,58; -14,69</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 7,44</t>
+          <t>-12,26; 6,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -22,48</t>
+          <t>-37,36; -22,39</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-22,84; -5,49</t>
+          <t>-23,31; -5,95</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 4,79</t>
+          <t>-7,04; 5,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 1,95</t>
+          <t>-10,64; 1,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 40,99</t>
+          <t>2,2; 41,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,73; -3,74</t>
+          <t>-16,4; -3,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -10,81</t>
+          <t>-22,28; -9,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,23; -3,43</t>
+          <t>-16,98; -3,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,28; -1,47</t>
+          <t>-10,11; -1,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -5,66</t>
+          <t>-14,37; -5,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 23,64</t>
+          <t>-3,57; 23,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 12,47</t>
+          <t>-15,42; 14,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 4,64</t>
+          <t>-22,41; 4,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,72; 98,31</t>
+          <t>5,04; 104,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,28; -6,44</t>
+          <t>-26,01; -6,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,38; -18,8</t>
+          <t>-35,5; -17,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,06; -6,21</t>
+          <t>-27,37; -6,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,28; -2,98</t>
+          <t>-19,18; -2,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; -11,29</t>
+          <t>-27,27; -11,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-7,17; 48,86</t>
+          <t>-6,84; 50,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -0,49</t>
+          <t>-13,8; 0,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -3,18</t>
+          <t>-16,4; -3,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,53; -1,75</t>
+          <t>-13,2; -1,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 6,84</t>
+          <t>-6,18; 6,9</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,17; -0,85</t>
+          <t>-14,04; -1,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,55; -1,29</t>
+          <t>-11,8; -1,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 1,33</t>
+          <t>-8,05; 1,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,22; -3,87</t>
+          <t>-13,29; -3,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -2,6</t>
+          <t>-11,05; -2,77</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,63; -0,69</t>
+          <t>-19,86; 0,3</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-24,43; -4,98</t>
+          <t>-23,84; -5,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -2,75</t>
+          <t>-18,94; -2,07</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 10,3</t>
+          <t>-8,6; 10,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-18,12; -1,25</t>
+          <t>-19,17; -1,99</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,64; -2,03</t>
+          <t>-15,76; -1,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 2,03</t>
+          <t>-11,45; 2,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -5,97</t>
+          <t>-18,96; -6,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -3,9</t>
+          <t>-15,6; -4,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 6,55</t>
+          <t>-7,07; 6,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,28; -0,96</t>
+          <t>-15,75; -1,6</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -7,53</t>
+          <t>-19,96; -7,42</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,72; -1,22</t>
+          <t>-12,11; -1,2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-15,71; -5,18</t>
+          <t>-16,58; -5,04</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 8,91</t>
+          <t>-12,42; 9,9</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 0,05</t>
+          <t>-8,71; 0,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -5,37</t>
+          <t>-14,07; -4,82</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 8,45</t>
+          <t>-13,91; 6,17</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 8,82</t>
+          <t>-8,98; 8,35</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,91; -1,27</t>
+          <t>-19,93; -2,2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,2; -10,46</t>
+          <t>-25,05; -10,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,25; -1,4</t>
+          <t>-13,23; -1,37</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-17,79; -6,12</t>
+          <t>-18,49; -5,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 10,57</t>
+          <t>-14,02; 12,08</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,07</t>
+          <t>-10,37; 0,11</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -6,55</t>
+          <t>-16,75; -6,26</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,23; 10,79</t>
+          <t>-16,73; 7,86</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 3,25</t>
+          <t>-9,62; 3,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,32; -2,85</t>
+          <t>-14,89; -2,74</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -4,17</t>
+          <t>-15,06; -4,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,95</t>
+          <t>-4,84; 2,15</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,75; -0,91</t>
+          <t>-8,78; -0,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,74; -0,79</t>
+          <t>-6,84; -0,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,07</t>
+          <t>-5,47; 0,82</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,82; -3,11</t>
+          <t>-9,41; -2,89</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -3,64</t>
+          <t>-9,36; -3,75</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 3,71</t>
+          <t>-10,41; 3,31</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-15,54; -3,41</t>
+          <t>-16,05; -3,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -4,84</t>
+          <t>-16,16; -4,77</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 2,06</t>
+          <t>-4,99; 2,22</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -1,0</t>
+          <t>-9,12; -0,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,91; -0,95</t>
+          <t>-6,92; -0,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 1,15</t>
+          <t>-5,79; 0,87</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-10,39; -3,39</t>
+          <t>-9,94; -3,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,51; -3,9</t>
+          <t>-9,79; -4,06</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,77</t>
+          <t>-0,97; 3,93</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -1,13</t>
+          <t>-6,05; -1,24</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,64; 19,39</t>
+          <t>2,56; 17,79</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,3</t>
+          <t>-5,05; -0,07</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,7; -6,83</t>
+          <t>-11,47; -6,64</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 6,39</t>
+          <t>-6,17; 5,95</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,06</t>
+          <t>-2,46; 0,96</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,16; -4,81</t>
+          <t>-8,14; -4,78</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,91</t>
+          <t>-0,96; 9,1</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 9,16</t>
+          <t>-2,2; 9,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -2,73</t>
+          <t>-13,79; -2,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6,17; 46,13</t>
+          <t>5,88; 41,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-9,0; -0,55</t>
+          <t>-8,72; -0,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-20,12; -12,3</t>
+          <t>-19,76; -11,82</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-11,14; 11,3</t>
+          <t>-10,94; 10,58</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,17</t>
+          <t>-4,85; 1,93</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -9,77</t>
+          <t>-16,08; -9,73</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 17,86</t>
+          <t>-1,89; 18,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/PCS12_SP_R2-Edad-trans_camb.xlsx
+++ b/data/trans_camb/PCS12_SP_R2-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,91</t>
+          <t>-1,93</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-9,89</t>
+          <t>-8,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-6,26</t>
+          <t>-5,13</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 7,35</t>
+          <t>-3,35; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,52</t>
+          <t>-9,36; 1,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 5,35</t>
+          <t>-9,14; 5,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,74</t>
+          <t>-6,26; 6,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -1,27</t>
+          <t>-12,38; -0,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,85; -1,58</t>
+          <t>-15,78; -1,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 5,23</t>
+          <t>-3,25; 4,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -1,54</t>
+          <t>-9,3; -1,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -0,28</t>
+          <t>-9,9; 0,7</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-13,12%</t>
+          <t>-8,72%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,12%</t>
+          <t>-30,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-24,95%</t>
+          <t>-20,46%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 36,38</t>
+          <t>-13,68; 38,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 7,93</t>
+          <t>-38,66; 5,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 26,54</t>
+          <t>-38,17; 29,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 22,69</t>
+          <t>-20,17; 24,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-40,07; -4,66</t>
+          <t>-41,15; -3,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-56,46; -6,23</t>
+          <t>-52,15; -5,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 22,53</t>
+          <t>-12,14; 21,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,12; -6,67</t>
+          <t>-34,28; -5,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-43,16; -0,73</t>
+          <t>-37,58; 3,36</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,23</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-13,63</t>
+          <t>-10,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-3,08</t>
+          <t>-1,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 9,06</t>
+          <t>-0,62; 9,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,09</t>
+          <t>-7,16; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 13,72</t>
+          <t>-0,63; 12,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 1,03</t>
+          <t>-9,98; 1,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -10,78</t>
+          <t>-21,66; -10,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-23,67; -6,61</t>
+          <t>-16,17; -4,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 4,11</t>
+          <t>-3,26; 4,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -4,92</t>
+          <t>-11,88; -4,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 1,7</t>
+          <t>-5,14; 3,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-34,57%</t>
+          <t>-26,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-9,93%</t>
+          <t>-4,69%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 42,43</t>
+          <t>-2,52; 43,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,8; 14,75</t>
+          <t>-27,42; 12,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 62,68</t>
+          <t>-2,28; 56,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-24,09; 2,55</t>
+          <t>-23,27; 3,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,73; -29,2</t>
+          <t>-51,02; -29,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-59,78; -17,99</t>
+          <t>-38,76; -12,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 14,27</t>
+          <t>-9,96; 14,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,29; -16,12</t>
+          <t>-36,35; -15,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 5,57</t>
+          <t>-16,15; 13,01</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-1,03</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,69</t>
+          <t>-11,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,18</t>
+          <t>-6,6</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,93</t>
+          <t>-3,48; 6,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,43; -5,23</t>
+          <t>-15,76; -5,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 5,47</t>
+          <t>-6,23; 4,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 1,63</t>
+          <t>-9,34; 1,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,98; -8,87</t>
+          <t>-19,57; -9,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,92; -6,74</t>
+          <t>-16,61; -6,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 2,54</t>
+          <t>-5,32; 2,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -8,92</t>
+          <t>-16,1; -8,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -2,4</t>
+          <t>-10,65; -2,74</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-0,41%</t>
+          <t>-3,03%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,12%</t>
+          <t>-23,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-14,88%</t>
+          <t>-15,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 22,42</t>
+          <t>-9,44; 21,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,93; -15,95</t>
+          <t>-43,0; -17,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-15,34; 17,07</t>
+          <t>-17,18; 13,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-18,43; 3,66</t>
+          <t>-18,42; 2,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-39,27; -19,29</t>
+          <t>-38,0; -19,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-32,58; -14,69</t>
+          <t>-32,59; -14,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 6,39</t>
+          <t>-12,34; 6,21</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-37,36; -22,39</t>
+          <t>-37,23; -21,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-23,31; -5,95</t>
+          <t>-24,47; -6,97</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19,03</t>
+          <t>4,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,16</t>
+          <t>-7,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>-1,72</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 5,75</t>
+          <t>-7,54; 4,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 1,56</t>
+          <t>-9,98; 1,76</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 41,83</t>
+          <t>-1,87; 9,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -3,98</t>
+          <t>-16,2; -4,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,28; -9,91</t>
+          <t>-22,8; -10,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,98; -3,84</t>
+          <t>-12,89; -2,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,11; -1,05</t>
+          <t>-10,07; -1,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -5,34</t>
+          <t>-14,72; -6,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 23,99</t>
+          <t>-6,12; 2,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-15,21%</t>
+          <t>-13,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>-3,35%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 14,73</t>
+          <t>-16,36; 11,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-22,41; 4,03</t>
+          <t>-22,51; 3,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,04; 104,87</t>
+          <t>-4,2; 24,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,01; -6,65</t>
+          <t>-25,81; -7,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,5; -17,77</t>
+          <t>-36,34; -18,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-27,37; -6,6</t>
+          <t>-20,33; -4,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,18; -2,16</t>
+          <t>-18,65; -2,51</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-27,27; -11,71</t>
+          <t>-27,28; -12,79</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 50,17</t>
+          <t>-11,4; 4,28</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-7,41</t>
+          <t>-9,09</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,58</t>
+          <t>-6,53</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-7,06</t>
+          <t>-7,85</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,16</t>
+          <t>-13,75; -0,74</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-16,4; -3,22</t>
+          <t>-16,64; -3,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -1,33</t>
+          <t>-15,55; -3,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 6,9</t>
+          <t>-5,74; 6,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-14,04; -1,36</t>
+          <t>-14,25; -1,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,8; -1,03</t>
+          <t>-11,47; -0,82</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,66</t>
+          <t>-8,05; 1,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-13,29; -3,91</t>
+          <t>-13,46; -4,23</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -2,77</t>
+          <t>-11,6; -3,61</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-11,19%</t>
+          <t>-13,73%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-9,34%</t>
+          <t>-9,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,33%</t>
+          <t>-11,48%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-19,86; 0,3</t>
+          <t>-19,88; -1,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-23,84; -5,08</t>
+          <t>-23,85; -5,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,94; -2,07</t>
+          <t>-22,26; -4,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 10,34</t>
+          <t>-7,76; 9,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-19,17; -1,99</t>
+          <t>-19,46; -2,05</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -1,51</t>
+          <t>-15,71; -1,27</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-11,45; 2,54</t>
+          <t>-11,49; 1,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,96; -6,05</t>
+          <t>-19,19; -6,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-15,6; -4,29</t>
+          <t>-16,41; -5,57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-13,95</t>
+          <t>-14,69</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,19</t>
+          <t>-11,43</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-13,19</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 6,03</t>
+          <t>-8,25; 5,54</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-15,75; -1,6</t>
+          <t>-15,11; -1,57</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,96; -7,42</t>
+          <t>-20,37; -7,91</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,11; -1,2</t>
+          <t>-12,22; -0,88</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,58; -5,04</t>
+          <t>-15,97; -4,71</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 9,9</t>
+          <t>-15,46; -6,78</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 0,08</t>
+          <t>-8,26; 0,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-14,07; -4,82</t>
+          <t>-14,16; -5,01</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 6,17</t>
+          <t>-17,04; -9,14</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-18,11%</t>
+          <t>-19,07%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-3,65%</t>
+          <t>-13,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-7,65%</t>
+          <t>-15,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 8,35</t>
+          <t>-10,09; 7,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-19,93; -2,2</t>
+          <t>-18,97; -2,16</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,05; -10,38</t>
+          <t>-25,56; -11,03</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,23; -1,37</t>
+          <t>-13,54; -1,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-18,49; -5,98</t>
+          <t>-17,98; -5,52</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 12,08</t>
+          <t>-17,48; -8,24</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 0,11</t>
+          <t>-9,85; 1,13</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -6,26</t>
+          <t>-16,83; -6,25</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 7,86</t>
+          <t>-20,18; -11,32</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-10,13</t>
+          <t>-10,63</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-4,24</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-6,57</t>
+          <t>-6,9</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,62; 3,02</t>
+          <t>-9,34; 3,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -2,74</t>
+          <t>-14,28; -2,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -4,03</t>
+          <t>-15,74; -5,3</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,15</t>
+          <t>-4,61; 1,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-8,78; -0,82</t>
+          <t>-8,33; -0,82</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,84; -0,91</t>
+          <t>-7,06; -1,12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 0,82</t>
+          <t>-5,37; 0,76</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-9,41; -2,89</t>
+          <t>-9,84; -2,86</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -3,75</t>
+          <t>-9,8; -3,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-11,16%</t>
+          <t>-11,72%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,22%</t>
+          <t>-4,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-6,99%</t>
+          <t>-7,35%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 3,31</t>
+          <t>-9,98; 3,48</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-16,05; -3,17</t>
+          <t>-15,36; -2,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,16; -4,77</t>
+          <t>-17,01; -6,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 2,22</t>
+          <t>-4,74; 2,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,12; -0,88</t>
+          <t>-8,62; -0,91</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -0,93</t>
+          <t>-7,28; -1,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 0,87</t>
+          <t>-5,62; 0,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -3,15</t>
+          <t>-10,3; -3,04</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-9,79; -4,06</t>
+          <t>-10,27; -4,29</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>7,22</t>
+          <t>2,9</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-2,33</t>
+          <t>-4,12</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 3,93</t>
+          <t>-1,03; 3,98</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,05; -1,24</t>
+          <t>-5,88; -1,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,56; 17,79</t>
+          <t>0,49; 5,45</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,07</t>
+          <t>-5,27; -0,42</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-11,47; -6,64</t>
+          <t>-11,41; -6,74</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 5,95</t>
+          <t>-6,22; -1,75</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,96</t>
+          <t>-2,44; 1,08</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-8,14; -4,78</t>
+          <t>-8,19; -4,72</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 9,1</t>
+          <t>-2,34; 1,15</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-4,09%</t>
+          <t>-7,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>-1,23%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 9,51</t>
+          <t>-2,37; 9,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -2,98</t>
+          <t>-13,47; -2,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5,88; 41,8</t>
+          <t>1,13; 13,2</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -0,14</t>
+          <t>-8,99; -0,74</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-19,76; -11,82</t>
+          <t>-19,85; -12,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 10,58</t>
+          <t>-10,65; -3,17</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 1,93</t>
+          <t>-4,77; 2,21</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -9,73</t>
+          <t>-16,04; -9,52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 18,35</t>
+          <t>-4,61; 2,38</t>
         </is>
       </c>
     </row>
